--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:43</t>
+    <t xml:space="preserve">2026-09-09 23:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:42</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:03</t>
+    <t xml:space="preserve">2026-10-02 15:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Mulchén</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Penco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:35</t>
+    <t xml:space="preserve">2026-10-04 09:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:48</t>
+    <t xml:space="preserve">2026-10-05 13:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
